--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654530</v>
+        <v>121654452</v>
       </c>
       <c r="B2" t="n">
-        <v>95660</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325690</v>
+        <v>325594</v>
       </c>
       <c r="R2" t="n">
-        <v>6551680</v>
+        <v>6551700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>15-20m2</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654452</v>
+        <v>121654531</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325594</v>
+        <v>325684</v>
       </c>
       <c r="R3" t="n">
-        <v>6551700</v>
+        <v>6551680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,17 +865,13 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>15-20m2</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,17 +883,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654545</v>
+        <v>121654451</v>
       </c>
       <c r="B4" t="n">
-        <v>95660</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325676</v>
+        <v>325561</v>
       </c>
       <c r="R4" t="n">
-        <v>6551751</v>
+        <v>6551690</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +960,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +990,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1088,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121654451</v>
+        <v>121654529</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>91484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,7 +1139,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325561</v>
+        <v>325687</v>
       </c>
       <c r="R6" t="n">
         <v>6551690</v>
@@ -1166,11 +1177,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1188,17 +1194,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121654529</v>
+        <v>121654545</v>
       </c>
       <c r="B7" t="n">
-        <v>91484</v>
+        <v>95660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>366</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325687</v>
+        <v>325676</v>
       </c>
       <c r="R7" t="n">
-        <v>6551690</v>
+        <v>6551751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1271,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654533</v>
+        <v>121654530</v>
       </c>
       <c r="B8" t="n">
-        <v>90498</v>
+        <v>95660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1315,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325546</v>
+        <v>325690</v>
       </c>
       <c r="R8" t="n">
-        <v>6551702</v>
+        <v>6551680</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654531</v>
+        <v>121654546</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>96380</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,39 +1421,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325684</v>
+        <v>325690</v>
       </c>
       <c r="R9" t="n">
-        <v>6551680</v>
+        <v>6551738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,12 +1475,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket betydelsefullaförekomster</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,7 +1494,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1507,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121654546</v>
+        <v>121654533</v>
       </c>
       <c r="B10" t="n">
-        <v>96380</v>
+        <v>90498</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,21 +1528,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325690</v>
+        <v>325546</v>
       </c>
       <c r="R10" t="n">
-        <v>6551738</v>
+        <v>6551702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,17 +1582,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket betydelsefullaförekomster</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654452</v>
+        <v>121654529</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>91484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325594</v>
+        <v>325687</v>
       </c>
       <c r="R2" t="n">
-        <v>6551700</v>
+        <v>6551690</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +753,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>15-20m2</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654531</v>
+        <v>121654451</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325684</v>
+        <v>325561</v>
       </c>
       <c r="R3" t="n">
-        <v>6551680</v>
+        <v>6551690</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,13 +855,17 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,17 +877,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654451</v>
+        <v>121654532</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325561</v>
+        <v>325608</v>
       </c>
       <c r="R4" t="n">
-        <v>6551690</v>
+        <v>6551680</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,11 +962,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -990,17 +979,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654532</v>
+        <v>121654531</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,35 +998,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325608</v>
+        <v>325684</v>
       </c>
       <c r="R5" t="n">
         <v>6551680</v>
@@ -1081,6 +1075,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121654529</v>
+        <v>121654533</v>
       </c>
       <c r="B6" t="n">
-        <v>91484</v>
+        <v>90498</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1106,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>366</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325687</v>
+        <v>325546</v>
       </c>
       <c r="R6" t="n">
-        <v>6551690</v>
+        <v>6551702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1196,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121654545</v>
+        <v>121654530</v>
       </c>
       <c r="B7" t="n">
         <v>95660</v>
@@ -1241,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325676</v>
+        <v>325690</v>
       </c>
       <c r="R7" t="n">
-        <v>6551751</v>
+        <v>6551680</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,12 +1266,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,7 +1298,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654530</v>
+        <v>121654545</v>
       </c>
       <c r="B8" t="n">
         <v>95660</v>
@@ -1343,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325690</v>
+        <v>325676</v>
       </c>
       <c r="R8" t="n">
-        <v>6551680</v>
+        <v>6551751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,12 +1368,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654546</v>
+        <v>121654452</v>
       </c>
       <c r="B9" t="n">
-        <v>96380</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,21 +1416,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325690</v>
+        <v>325594</v>
       </c>
       <c r="R9" t="n">
-        <v>6551738</v>
+        <v>6551700</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,17 +1470,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mycket betydelsefullaförekomster</t>
+          <t>15-20m2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,17 +1500,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121654533</v>
+        <v>121654546</v>
       </c>
       <c r="B10" t="n">
-        <v>90498</v>
+        <v>96380</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325546</v>
+        <v>325690</v>
       </c>
       <c r="R10" t="n">
-        <v>6551702</v>
+        <v>6551738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,12 +1577,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket betydelsefullaförekomster</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654529</v>
+        <v>121654546</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>96380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325687</v>
+        <v>325690</v>
       </c>
       <c r="R2" t="n">
-        <v>6551690</v>
+        <v>6551738</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mycket betydelsefullaförekomster</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654451</v>
+        <v>121654532</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325561</v>
+        <v>325608</v>
       </c>
       <c r="R3" t="n">
-        <v>6551690</v>
+        <v>6551680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +860,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -877,17 +877,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654532</v>
+        <v>121654451</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325608</v>
+        <v>325561</v>
       </c>
       <c r="R4" t="n">
-        <v>6551680</v>
+        <v>6551690</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,6 +962,11 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -979,17 +984,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654531</v>
+        <v>121654545</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>95660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,43 +1003,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325684</v>
+        <v>325676</v>
       </c>
       <c r="R5" t="n">
-        <v>6551680</v>
+        <v>6551751</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,7 +1075,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1298,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654545</v>
+        <v>121654452</v>
       </c>
       <c r="B8" t="n">
-        <v>95660</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1310,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325676</v>
+        <v>325594</v>
       </c>
       <c r="R8" t="n">
-        <v>6551751</v>
+        <v>6551700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,12 +1367,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>15-20m2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,17 +1397,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654452</v>
+        <v>121654529</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>91484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325594</v>
+        <v>325687</v>
       </c>
       <c r="R9" t="n">
-        <v>6551700</v>
+        <v>6551690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,11 +1482,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>15-20m2</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1500,17 +1499,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121654546</v>
+        <v>121654531</v>
       </c>
       <c r="B10" t="n">
-        <v>96380</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,34 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325690</v>
+        <v>325684</v>
       </c>
       <c r="R10" t="n">
-        <v>6551738</v>
+        <v>6551680</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,17 +1581,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket betydelsefullaförekomster</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,6 +1595,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654546</v>
+        <v>121654531</v>
       </c>
       <c r="B2" t="n">
-        <v>96380</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325690</v>
+        <v>325684</v>
       </c>
       <c r="R2" t="n">
-        <v>6551738</v>
+        <v>6551680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mycket betydelsefullaförekomster</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654532</v>
+        <v>121654530</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>95660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,7 +823,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325608</v>
+        <v>325690</v>
       </c>
       <c r="R3" t="n">
         <v>6551680</v>
@@ -884,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654451</v>
+        <v>121654452</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +897,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325561</v>
+        <v>325594</v>
       </c>
       <c r="R4" t="n">
-        <v>6551690</v>
+        <v>6551700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +965,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosöksspår</t>
+          <t>15-20m2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654545</v>
+        <v>121654532</v>
       </c>
       <c r="B5" t="n">
-        <v>95660</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1008,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325676</v>
+        <v>325608</v>
       </c>
       <c r="R5" t="n">
-        <v>6551751</v>
+        <v>6551680</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121654533</v>
+        <v>121654529</v>
       </c>
       <c r="B6" t="n">
-        <v>90498</v>
+        <v>91484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1106,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325546</v>
+        <v>325687</v>
       </c>
       <c r="R6" t="n">
-        <v>6551702</v>
+        <v>6551690</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121654530</v>
+        <v>121654451</v>
       </c>
       <c r="B7" t="n">
-        <v>95660</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325690</v>
+        <v>325561</v>
       </c>
       <c r="R7" t="n">
-        <v>6551680</v>
+        <v>6551690</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,6 +1274,11 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1290,17 +1296,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654452</v>
+        <v>121654533</v>
       </c>
       <c r="B8" t="n">
-        <v>97067</v>
+        <v>90498</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1319,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325594</v>
+        <v>325546</v>
       </c>
       <c r="R8" t="n">
-        <v>6551700</v>
+        <v>6551702</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,11 +1381,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>15-20m2</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1397,17 +1398,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654529</v>
+        <v>121654545</v>
       </c>
       <c r="B9" t="n">
-        <v>91484</v>
+        <v>95660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1421,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>366</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325687</v>
+        <v>325676</v>
       </c>
       <c r="R9" t="n">
-        <v>6551690</v>
+        <v>6551751</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,12 +1475,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121654531</v>
+        <v>121654546</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>96380</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,39 +1523,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325684</v>
+        <v>325690</v>
       </c>
       <c r="R10" t="n">
-        <v>6551680</v>
+        <v>6551738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,12 +1577,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket betydelsefullaförekomster</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,7 +1596,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654531</v>
+        <v>121654530</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>95660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325684</v>
+        <v>325690</v>
       </c>
       <c r="R2" t="n">
         <v>6551680</v>
@@ -764,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654530</v>
+        <v>121654533</v>
       </c>
       <c r="B3" t="n">
-        <v>95660</v>
+        <v>90498</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325690</v>
+        <v>325546</v>
       </c>
       <c r="R3" t="n">
-        <v>6551680</v>
+        <v>6551702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -992,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654532</v>
+        <v>121654451</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325608</v>
+        <v>325561</v>
       </c>
       <c r="R5" t="n">
-        <v>6551680</v>
+        <v>6551690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,6 +1064,11 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1087,17 +1086,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121654529</v>
+        <v>121654546</v>
       </c>
       <c r="B6" t="n">
-        <v>91484</v>
+        <v>96380</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1106,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>366</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325687</v>
+        <v>325690</v>
       </c>
       <c r="R6" t="n">
-        <v>6551690</v>
+        <v>6551738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1163,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mycket betydelsefullaförekomster</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121654451</v>
+        <v>121654529</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>91484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,7 +1240,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325561</v>
+        <v>325687</v>
       </c>
       <c r="R7" t="n">
         <v>6551690</v>
@@ -1274,11 +1278,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1296,17 +1295,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654533</v>
+        <v>121654531</v>
       </c>
       <c r="B8" t="n">
-        <v>90498</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,34 +1318,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325546</v>
+        <v>325684</v>
       </c>
       <c r="R8" t="n">
-        <v>6551702</v>
+        <v>6551680</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1391,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1507,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121654546</v>
+        <v>121654532</v>
       </c>
       <c r="B10" t="n">
-        <v>96380</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1519,25 +1524,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325690</v>
+        <v>325608</v>
       </c>
       <c r="R10" t="n">
-        <v>6551738</v>
+        <v>6551680</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,17 +1582,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket betydelsefullaförekomster</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654530</v>
+        <v>121654452</v>
       </c>
       <c r="B2" t="n">
-        <v>95660</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325690</v>
+        <v>325594</v>
       </c>
       <c r="R2" t="n">
-        <v>6551680</v>
+        <v>6551700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>15-20m2</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654533</v>
+        <v>121654530</v>
       </c>
       <c r="B3" t="n">
-        <v>90498</v>
+        <v>95660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325546</v>
+        <v>325690</v>
       </c>
       <c r="R3" t="n">
-        <v>6551702</v>
+        <v>6551680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654452</v>
+        <v>121654533</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>90498</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325594</v>
+        <v>325546</v>
       </c>
       <c r="R4" t="n">
-        <v>6551700</v>
+        <v>6551702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,11 +962,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>15-20m2</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -979,7 +979,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654452</v>
+        <v>121654532</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325594</v>
+        <v>325608</v>
       </c>
       <c r="R2" t="n">
-        <v>6551700</v>
+        <v>6551680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +753,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>15-20m2</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654530</v>
+        <v>121654451</v>
       </c>
       <c r="B3" t="n">
-        <v>95660</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325690</v>
+        <v>325561</v>
       </c>
       <c r="R3" t="n">
-        <v>6551680</v>
+        <v>6551690</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,6 +855,11 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -877,17 +877,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654533</v>
+        <v>121654546</v>
       </c>
       <c r="B4" t="n">
-        <v>90498</v>
+        <v>96380</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325546</v>
+        <v>325690</v>
       </c>
       <c r="R4" t="n">
-        <v>6551702</v>
+        <v>6551738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +954,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket betydelsefullaförekomster</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654451</v>
+        <v>121654530</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>95660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325561</v>
+        <v>325690</v>
       </c>
       <c r="R5" t="n">
-        <v>6551690</v>
+        <v>6551680</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,11 +1069,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1086,17 +1086,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121654546</v>
+        <v>121654452</v>
       </c>
       <c r="B6" t="n">
-        <v>96380</v>
+        <v>97067</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325690</v>
+        <v>325594</v>
       </c>
       <c r="R6" t="n">
-        <v>6551738</v>
+        <v>6551700</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,17 +1163,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Mycket betydelsefullaförekomster</t>
+          <t>15-20m2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654531</v>
+        <v>121654545</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>95660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,43 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325684</v>
+        <v>325676</v>
       </c>
       <c r="R8" t="n">
-        <v>6551680</v>
+        <v>6551751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,12 +1372,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,7 +1386,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1410,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654545</v>
+        <v>121654533</v>
       </c>
       <c r="B9" t="n">
-        <v>95660</v>
+        <v>90498</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1450,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325676</v>
+        <v>325546</v>
       </c>
       <c r="R9" t="n">
-        <v>6551751</v>
+        <v>6551702</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,12 +1474,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121654532</v>
+        <v>121654531</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1524,35 +1518,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325608</v>
+        <v>325684</v>
       </c>
       <c r="R10" t="n">
         <v>6551680</v>
@@ -1596,6 +1595,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654532</v>
+        <v>121654530</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>95678</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325608</v>
+        <v>325690</v>
       </c>
       <c r="R2" t="n">
         <v>6551680</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654451</v>
+        <v>121654529</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>91498</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325561</v>
+        <v>325687</v>
       </c>
       <c r="R3" t="n">
         <v>6551690</v>
@@ -855,11 +855,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -877,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654546</v>
+        <v>121654451</v>
       </c>
       <c r="B4" t="n">
-        <v>96380</v>
+        <v>57381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325690</v>
+        <v>325561</v>
       </c>
       <c r="R4" t="n">
-        <v>6551738</v>
+        <v>6551690</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,17 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mycket betydelsefullaförekomster</t>
+          <t>Födosöksspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,17 +979,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654530</v>
+        <v>121654531</v>
       </c>
       <c r="B5" t="n">
-        <v>95660</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,35 +998,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325690</v>
+        <v>325684</v>
       </c>
       <c r="R5" t="n">
         <v>6551680</v>
@@ -1075,6 +1075,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121654452</v>
+        <v>121654545</v>
       </c>
       <c r="B6" t="n">
-        <v>97067</v>
+        <v>95678</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1106,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325594</v>
+        <v>325676</v>
       </c>
       <c r="R6" t="n">
-        <v>6551700</v>
+        <v>6551751</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,17 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>15-20m2</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,17 +1189,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121654529</v>
+        <v>121654532</v>
       </c>
       <c r="B7" t="n">
-        <v>91484</v>
+        <v>78629</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>366</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325687</v>
+        <v>325608</v>
       </c>
       <c r="R7" t="n">
-        <v>6551690</v>
+        <v>6551680</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654545</v>
+        <v>121654546</v>
       </c>
       <c r="B8" t="n">
-        <v>95660</v>
+        <v>96398</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1310,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325676</v>
+        <v>325690</v>
       </c>
       <c r="R8" t="n">
-        <v>6551751</v>
+        <v>6551738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1374,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mycket betydelsefullaförekomster</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654533</v>
+        <v>121654452</v>
       </c>
       <c r="B9" t="n">
-        <v>90498</v>
+        <v>97085</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1421,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325546</v>
+        <v>325594</v>
       </c>
       <c r="R9" t="n">
-        <v>6551702</v>
+        <v>6551700</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,6 +1483,11 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>15-20m2</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1499,17 +1505,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121654531</v>
+        <v>121654533</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>90512</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,39 +1528,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325684</v>
+        <v>325546</v>
       </c>
       <c r="R10" t="n">
-        <v>6551680</v>
+        <v>6551702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1596,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121654530</v>
       </c>
       <c r="B2" t="n">
-        <v>95678</v>
+        <v>95680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654529</v>
+        <v>121654451</v>
       </c>
       <c r="B3" t="n">
-        <v>91498</v>
+        <v>57381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325687</v>
+        <v>325561</v>
       </c>
       <c r="R3" t="n">
         <v>6551690</v>
@@ -855,6 +855,11 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,17 +877,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654451</v>
+        <v>121654529</v>
       </c>
       <c r="B4" t="n">
-        <v>57381</v>
+        <v>91500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +924,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325561</v>
+        <v>325687</v>
       </c>
       <c r="R4" t="n">
         <v>6551690</v>
@@ -957,11 +962,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -979,17 +979,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654531</v>
+        <v>121654545</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>95680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325684</v>
+        <v>325676</v>
       </c>
       <c r="R5" t="n">
-        <v>6551680</v>
+        <v>6551751</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,7 +1070,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1094,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121654545</v>
+        <v>121654533</v>
       </c>
       <c r="B6" t="n">
-        <v>95678</v>
+        <v>90514</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1106,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325676</v>
+        <v>325546</v>
       </c>
       <c r="R6" t="n">
-        <v>6551751</v>
+        <v>6551702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1193,7 @@
         <v>121654532</v>
       </c>
       <c r="B7" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654546</v>
+        <v>121654452</v>
       </c>
       <c r="B8" t="n">
-        <v>96398</v>
+        <v>97087</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325690</v>
+        <v>325594</v>
       </c>
       <c r="R8" t="n">
-        <v>6551738</v>
+        <v>6551700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,17 +1362,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mycket betydelsefullaförekomster</t>
+          <t>15-20m2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,17 +1392,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654452</v>
+        <v>121654531</v>
       </c>
       <c r="B9" t="n">
-        <v>97085</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,34 +1415,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325594</v>
+        <v>325684</v>
       </c>
       <c r="R9" t="n">
-        <v>6551700</v>
+        <v>6551680</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,17 +1482,13 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>15-20m2</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1505,17 +1500,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121654533</v>
+        <v>121654546</v>
       </c>
       <c r="B10" t="n">
-        <v>90512</v>
+        <v>96666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325546</v>
+        <v>325690</v>
       </c>
       <c r="R10" t="n">
-        <v>6551702</v>
+        <v>6551738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,12 +1577,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket betydelsefullaförekomster</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654530</v>
+        <v>121654452</v>
       </c>
       <c r="B2" t="n">
-        <v>95680</v>
+        <v>97094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325690</v>
+        <v>325594</v>
       </c>
       <c r="R2" t="n">
-        <v>6551680</v>
+        <v>6551700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2024-10-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>15-20m2</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654451</v>
+        <v>121654546</v>
       </c>
       <c r="B3" t="n">
-        <v>57381</v>
+        <v>96673</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325561</v>
+        <v>325690</v>
       </c>
       <c r="R3" t="n">
-        <v>6551690</v>
+        <v>6551738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,17 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosöksspår</t>
+          <t>Mycket betydelsefullaförekomster</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654529</v>
+        <v>121654531</v>
       </c>
       <c r="B4" t="n">
-        <v>91500</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>366</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325687</v>
+        <v>325684</v>
       </c>
       <c r="R4" t="n">
-        <v>6551690</v>
+        <v>6551680</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +978,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -986,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654545</v>
+        <v>121654533</v>
       </c>
       <c r="B5" t="n">
-        <v>95680</v>
+        <v>90515</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1009,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325676</v>
+        <v>325546</v>
       </c>
       <c r="R5" t="n">
-        <v>6551751</v>
+        <v>6551702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121654533</v>
+        <v>121654530</v>
       </c>
       <c r="B6" t="n">
-        <v>90514</v>
+        <v>95687</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325546</v>
+        <v>325690</v>
       </c>
       <c r="R6" t="n">
-        <v>6551702</v>
+        <v>6551680</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1204,7 @@
         <v>121654532</v>
       </c>
       <c r="B7" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654452</v>
+        <v>121654451</v>
       </c>
       <c r="B8" t="n">
-        <v>97087</v>
+        <v>57381</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1315,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325594</v>
+        <v>325561</v>
       </c>
       <c r="R8" t="n">
-        <v>6551700</v>
+        <v>6551690</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1383,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>15-20m2</t>
+          <t>Födosöksspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654531</v>
+        <v>121654545</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>95687</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,43 +1422,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325684</v>
+        <v>325676</v>
       </c>
       <c r="R9" t="n">
-        <v>6551680</v>
+        <v>6551751</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,12 +1480,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,7 +1494,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1507,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121654546</v>
+        <v>121654529</v>
       </c>
       <c r="B10" t="n">
-        <v>96666</v>
+        <v>91501</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1519,25 +1524,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325690</v>
+        <v>325687</v>
       </c>
       <c r="R10" t="n">
-        <v>6551738</v>
+        <v>6551690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,17 +1582,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket betydelsefullaförekomster</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121654452</v>
+        <v>121654530</v>
       </c>
       <c r="B2" t="n">
-        <v>97094</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325594</v>
+        <v>325690</v>
       </c>
       <c r="R2" t="n">
-        <v>6551700</v>
+        <v>6551680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +748,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>15-20m2</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,44 +765,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654546</v>
+        <v>121654537</v>
       </c>
       <c r="B3" t="n">
-        <v>96673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325690</v>
+        <v>325565</v>
       </c>
       <c r="R3" t="n">
-        <v>6551738</v>
+        <v>6551741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mycket betydelsefullaförekomster</t>
+          <t>Betydelsefulla förekomster</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,55 +874,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654531</v>
+        <v>121654545</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325684</v>
+        <v>325676</v>
       </c>
       <c r="R4" t="n">
-        <v>6551680</v>
+        <v>6551751</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,12 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,7 +953,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,37 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654533</v>
+        <v>121654529</v>
       </c>
       <c r="B5" t="n">
-        <v>90515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325546</v>
+        <v>325687</v>
       </c>
       <c r="R5" t="n">
-        <v>6551702</v>
+        <v>6551690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,37 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121654530</v>
+        <v>121654546</v>
       </c>
       <c r="B6" t="n">
-        <v>95687</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,7 +1106,7 @@
         <v>325690</v>
       </c>
       <c r="R6" t="n">
-        <v>6551680</v>
+        <v>6551738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1133,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mycket betydelsefullaförekomster</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,37 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121654532</v>
+        <v>121654528</v>
       </c>
       <c r="B7" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325608</v>
+        <v>325697</v>
       </c>
       <c r="R7" t="n">
-        <v>6551680</v>
+        <v>6551760</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Betydelsefulla förekomster</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,37 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654451</v>
+        <v>121654533</v>
       </c>
       <c r="B8" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325561</v>
+        <v>325546</v>
       </c>
       <c r="R8" t="n">
-        <v>6551690</v>
+        <v>6551702</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,11 +1345,6 @@
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1403,44 +1362,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654545</v>
+        <v>121654532</v>
       </c>
       <c r="B9" t="n">
-        <v>95687</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1450,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325676</v>
+        <v>325608</v>
       </c>
       <c r="R9" t="n">
-        <v>6551751</v>
+        <v>6551680</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,12 +1434,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,15 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121654529</v>
+        <v>121654548</v>
       </c>
       <c r="B10" t="n">
-        <v>91501</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,21 +1477,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>366</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325687</v>
+        <v>325720</v>
       </c>
       <c r="R10" t="n">
-        <v>6551690</v>
+        <v>6551760</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,12 +1531,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,6 +1560,313 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121654451</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>325561</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6551690</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121654531</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>325684</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6551680</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121654452</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>325594</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6551700</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>15-20m2</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42944-2022 artfynd.xlsx
+++ b/artfynd/A 42944-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654530</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654537</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654545</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654529</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654546</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654528</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654533</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654532</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654548</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654451</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1765,6 +1820,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654531</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1867,8 +1927,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654452</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>